--- a/02_DIA_inicio_2026_analisis_assets/rbd_9611_escuela-basica-tupahue_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9611_escuela-basica-tupahue_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C5691ED-066A-43AD-A56D-FC268408CBA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93DFB284-F808-4BB0-AC13-B5A530C87F06}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F134FE8B-7E5C-4E15-BE90-7D77987D6BE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D0F6499-13E5-4F96-BBF7-4D1281BE079A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A879641-5522-4334-BB3D-2CE907744558}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8923A0A8-166F-412A-8721-AC36B8A77369}"/>
 </file>